--- a/DateBase/orders/Nhat 48_2026-10-20.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-20.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -526,10 +526,48 @@
       <c r="C11" t="str">
         <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F12" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>4</v>
+      </c>
+      <c r="C14" t="str">
+        <v>388_大丽花_dahlia_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>590_洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -584,7 +622,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>067591088620150</v>
+        <v>0675910886201510810156</v>
       </c>
     </row>
   </sheetData>
